--- a/GV.xlsx
+++ b/GV.xlsx
@@ -1,39 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D46E1C-E6A0-4FE4-B2BF-CBB730C9CF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="GIAOVIEN" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="LINHVUC" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="TIEUCHI" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="MINHCHUNG" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="HOME" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="DANHGIA" sheetId="6" r:id="rId10"/>
+    <sheet name="GIAOVIEN" sheetId="1" r:id="rId1"/>
+    <sheet name="LINHVUC" sheetId="2" r:id="rId2"/>
+    <sheet name="TIEUCHI" sheetId="3" r:id="rId3"/>
+    <sheet name="MINHCHUNG" sheetId="4" r:id="rId4"/>
+    <sheet name="HOME" sheetId="5" r:id="rId5"/>
+    <sheet name="DANHGIA" sheetId="6" r:id="rId6"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
     <author>tc={f8194994-d815-4405-be1a-a961e4b6191f}</author>
   </authors>
   <commentList>
-    <comment authorId="0" ref="F4">
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
-        <t xml:space="preserve">ttthuedtnt@gmail.com</t>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ttthuedtnt@gmail.com</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{f8194994-d815-4405-be1a-a961e4b6191f}" ref="F30">
+    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{F8194994-D815-4405-BE1A-A961E4B6191F}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	lythanhcandtnt@gmail.com
-</t>
+    lythanhcandtnt@gmail.com</t>
       </text>
     </comment>
   </commentList>
@@ -874,34 +890,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="5">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="&quot;Times New Roman&quot;"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -912,11 +930,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -930,74 +954,44 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
-<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks"/>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Cần Lý Thanh" id="{82e98797-daf0-40ef-b80f-2866a5e878b1}" providerId="google-sheets"/>
-</x18tc:personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Cần Lý Thanh" id="{82E98797-DAF0-40EF-B80F-2866A5E878B1}" userId="" providerId="google-sheets"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1187,32 +1181,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="F30" dT="2026-07-22T01:44:35.00" personId="{82e98797-daf0-40ef-b80f-2866a5e878b1}" id="{f8194994-d815-4405-be1a-a961e4b6191f}" done="0">
-    <x18tc:text xml:space="preserve">lythanhcandtnt@gmail.com</x18tc:text>
-  </x18tc:threadedComment>
-</x18tc:ThreadedComments>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F30" dT="2026-07-22T01:44:35.00" personId="{82E98797-DAF0-40EF-B80F-2866A5E878B1}" id="{F8194994-D815-4405-BE1A-A961E4B6191F}">
+    <text>lythanhcandtnt@gmail.com</text>
+  </threadedComment>
+</ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.63"/>
-    <col customWidth="1" min="2" max="2" width="25.0"/>
-    <col customWidth="1" min="3" max="3" width="24.25"/>
-    <col customWidth="1" min="5" max="5" width="29.13"/>
-    <col customWidth="1" min="6" max="6" width="39.0"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="5" max="5" width="29.109375" customWidth="1"/>
+    <col min="6" max="6" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="13.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1232,7 +1229,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="13.2">
       <c r="A2" s="1" t="s">
         <v>32</v>
       </c>
@@ -1246,13 +1243,13 @@
         <v>38</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="13.2">
       <c r="A3" s="1" t="s">
         <v>44</v>
       </c>
@@ -1272,7 +1269,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" ht="27.0" customHeight="1">
+    <row r="4" spans="1:6" ht="27" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
@@ -1292,7 +1289,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="13.2">
       <c r="A5" s="1" t="s">
         <v>57</v>
       </c>
@@ -1312,7 +1309,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" ht="13.2">
       <c r="A6" s="1" t="s">
         <v>62</v>
       </c>
@@ -1332,7 +1329,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" ht="13.2">
       <c r="A7" s="1" t="s">
         <v>68</v>
       </c>
@@ -1352,7 +1349,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" ht="13.2">
       <c r="A8" s="1" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1369,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" ht="13.2">
       <c r="A9" s="1" t="s">
         <v>83</v>
       </c>
@@ -1392,7 +1389,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" ht="13.2">
       <c r="A10" s="1" t="s">
         <v>87</v>
       </c>
@@ -1412,7 +1409,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" ht="13.2">
       <c r="A11" s="1" t="s">
         <v>95</v>
       </c>
@@ -1432,7 +1429,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" ht="13.2">
       <c r="A12" s="1" t="s">
         <v>101</v>
       </c>
@@ -1452,7 +1449,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" ht="13.2">
       <c r="A13" s="1" t="s">
         <v>108</v>
       </c>
@@ -1472,7 +1469,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" ht="13.2">
       <c r="A14" s="1" t="s">
         <v>118</v>
       </c>
@@ -1492,7 +1489,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" ht="13.2">
       <c r="A15" s="1" t="s">
         <v>127</v>
       </c>
@@ -1512,7 +1509,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" ht="13.2">
       <c r="A16" s="1" t="s">
         <v>133</v>
       </c>
@@ -1532,7 +1529,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" ht="13.2">
       <c r="A17" s="1" t="s">
         <v>140</v>
       </c>
@@ -1552,7 +1549,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" ht="13.2">
       <c r="A18" s="1" t="s">
         <v>146</v>
       </c>
@@ -1572,7 +1569,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" ht="13.2">
       <c r="A19" s="1" t="s">
         <v>151</v>
       </c>
@@ -1592,7 +1589,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" ht="13.2">
       <c r="A20" s="1" t="s">
         <v>157</v>
       </c>
@@ -1612,7 +1609,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" ht="13.2">
       <c r="A21" s="1" t="s">
         <v>164</v>
       </c>
@@ -1632,7 +1629,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" ht="13.2">
       <c r="A22" s="1" t="s">
         <v>171</v>
       </c>
@@ -1652,7 +1649,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" ht="13.2">
       <c r="A23" s="1" t="s">
         <v>176</v>
       </c>
@@ -1672,7 +1669,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" ht="13.2">
       <c r="A24" s="1" t="s">
         <v>181</v>
       </c>
@@ -1692,7 +1689,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" ht="13.2">
       <c r="A25" s="1" t="s">
         <v>188</v>
       </c>
@@ -1712,7 +1709,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" ht="13.2">
       <c r="A26" s="1" t="s">
         <v>195</v>
       </c>
@@ -1732,7 +1729,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" ht="13.2">
       <c r="A27" s="1" t="s">
         <v>200</v>
       </c>
@@ -1752,7 +1749,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" ht="13.2">
       <c r="A28" s="1" t="s">
         <v>205</v>
       </c>
@@ -1772,7 +1769,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" ht="13.2">
       <c r="A29" s="1" t="s">
         <v>211</v>
       </c>
@@ -1792,7 +1789,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6" ht="13.2">
       <c r="A30" s="1" t="s">
         <v>218</v>
       </c>
@@ -1812,7 +1809,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:6" ht="13.2">
       <c r="A31" s="1" t="s">
         <v>231</v>
       </c>
@@ -1832,7 +1829,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6" ht="13.2">
       <c r="A32" s="1" t="s">
         <v>237</v>
       </c>
@@ -1852,7 +1849,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:6" ht="13.2">
       <c r="A33" s="1" t="s">
         <v>243</v>
       </c>
@@ -1872,7 +1869,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6" ht="13.2">
       <c r="A34" s="1" t="s">
         <v>250</v>
       </c>
@@ -1892,7 +1889,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6" ht="13.2">
       <c r="A35" s="1" t="s">
         <v>254</v>
       </c>
@@ -1912,7 +1909,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6" ht="13.2">
       <c r="A36" s="1" t="s">
         <v>258</v>
       </c>
@@ -1932,7 +1929,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6" ht="13.2">
       <c r="A37" s="1" t="s">
         <v>261</v>
       </c>
@@ -1952,7 +1949,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:6" ht="13.2">
       <c r="A38" s="1" t="s">
         <v>265</v>
       </c>
@@ -1973,22 +1970,23 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId4"/>
-  <legacyDrawing r:id="rId5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="34.75"/>
+    <col min="2" max="2" width="34.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1996,7 +1994,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -2004,7 +2002,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -2012,7 +2010,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -2020,7 +2018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -2028,7 +2026,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -2036,7 +2034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -2044,7 +2042,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -2052,7 +2050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -2061,21 +2059,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="66.63"/>
+    <col min="3" max="3" width="66.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -2089,7 +2088,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>47</v>
       </c>
@@ -2100,10 +2099,10 @@
         <v>52</v>
       </c>
       <c r="D2" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>72</v>
       </c>
@@ -2114,10 +2113,10 @@
         <v>82</v>
       </c>
       <c r="D3" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>91</v>
       </c>
@@ -2128,10 +2127,10 @@
         <v>94</v>
       </c>
       <c r="D4" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>97</v>
       </c>
@@ -2142,10 +2141,10 @@
         <v>98</v>
       </c>
       <c r="D5" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>73</v>
       </c>
@@ -2156,10 +2155,10 @@
         <v>103</v>
       </c>
       <c r="D6" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>104</v>
       </c>
@@ -2170,10 +2169,10 @@
         <v>107</v>
       </c>
       <c r="D7" s="1">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>110</v>
       </c>
@@ -2184,10 +2183,10 @@
         <v>114</v>
       </c>
       <c r="D8" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>117</v>
       </c>
@@ -2198,10 +2197,10 @@
         <v>121</v>
       </c>
       <c r="D9" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>88</v>
       </c>
@@ -2212,10 +2211,10 @@
         <v>126</v>
       </c>
       <c r="D10" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>129</v>
       </c>
@@ -2226,10 +2225,10 @@
         <v>130</v>
       </c>
       <c r="D11" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>132</v>
       </c>
@@ -2240,10 +2239,10 @@
         <v>136</v>
       </c>
       <c r="D12" s="1">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>137</v>
       </c>
@@ -2254,10 +2253,10 @@
         <v>139</v>
       </c>
       <c r="D13" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>142</v>
       </c>
@@ -2268,10 +2267,10 @@
         <v>143</v>
       </c>
       <c r="D14" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>145</v>
       </c>
@@ -2282,10 +2281,10 @@
         <v>148</v>
       </c>
       <c r="D15" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>149</v>
       </c>
@@ -2296,10 +2295,10 @@
         <v>152</v>
       </c>
       <c r="D16" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>154</v>
       </c>
@@ -2310,10 +2309,10 @@
         <v>158</v>
       </c>
       <c r="D17" s="1">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>162</v>
       </c>
@@ -2324,10 +2323,10 @@
         <v>165</v>
       </c>
       <c r="D18" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>168</v>
       </c>
@@ -2338,10 +2337,10 @@
         <v>170</v>
       </c>
       <c r="D19" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>173</v>
       </c>
@@ -2352,10 +2351,10 @@
         <v>175</v>
       </c>
       <c r="D20" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>178</v>
       </c>
@@ -2366,10 +2365,10 @@
         <v>180</v>
       </c>
       <c r="D21" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>183</v>
       </c>
@@ -2380,10 +2379,10 @@
         <v>187</v>
       </c>
       <c r="D22" s="1">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>191</v>
       </c>
@@ -2394,10 +2393,10 @@
         <v>193</v>
       </c>
       <c r="D23" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>197</v>
       </c>
@@ -2408,10 +2407,10 @@
         <v>198</v>
       </c>
       <c r="D24" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>201</v>
       </c>
@@ -2422,10 +2421,10 @@
         <v>203</v>
       </c>
       <c r="D25" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>206</v>
       </c>
@@ -2436,10 +2435,10 @@
         <v>208</v>
       </c>
       <c r="D26" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>210</v>
       </c>
@@ -2450,10 +2449,10 @@
         <v>214</v>
       </c>
       <c r="D27" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>215</v>
       </c>
@@ -2464,10 +2463,10 @@
         <v>217</v>
       </c>
       <c r="D28" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>221</v>
       </c>
@@ -2478,10 +2477,10 @@
         <v>224</v>
       </c>
       <c r="D29" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>226</v>
       </c>
@@ -2492,10 +2491,10 @@
         <v>227</v>
       </c>
       <c r="D30" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>115</v>
       </c>
@@ -2506,10 +2505,10 @@
         <v>229</v>
       </c>
       <c r="D31" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="16.8">
       <c r="A32" s="1" t="s">
         <v>230</v>
       </c>
@@ -2520,10 +2519,10 @@
         <v>233</v>
       </c>
       <c r="D32" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="16.8">
       <c r="A33" s="1" t="s">
         <v>234</v>
       </c>
@@ -2534,10 +2533,10 @@
         <v>236</v>
       </c>
       <c r="D33" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="16.8">
       <c r="A34" s="1" t="s">
         <v>239</v>
       </c>
@@ -2548,10 +2547,10 @@
         <v>240</v>
       </c>
       <c r="D34" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="16.8">
       <c r="A35" s="1" t="s">
         <v>242</v>
       </c>
@@ -2562,10 +2561,10 @@
         <v>246</v>
       </c>
       <c r="D35" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="16.8">
       <c r="A36" s="1" t="s">
         <v>248</v>
       </c>
@@ -2576,28 +2575,29 @@
         <v>251</v>
       </c>
       <c r="D36" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="22.25"/>
-    <col customWidth="1" min="4" max="4" width="32.38"/>
-    <col customWidth="1" min="6" max="6" width="21.5"/>
-    <col customWidth="1" min="7" max="7" width="50.63"/>
+    <col min="3" max="3" width="22.21875" customWidth="1"/>
+    <col min="4" max="4" width="32.33203125" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="7" max="7" width="50.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>43</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>47</v>
       </c>
       <c r="D2" s="2">
-        <v>46225.0</v>
+        <v>46225</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>61</v>
@@ -2658,10 +2658,10 @@
         <v>66</v>
       </c>
       <c r="J2" s="2">
-        <v>46226.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>70</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>73</v>
       </c>
       <c r="D3" s="2">
-        <v>46225.0</v>
+        <v>46225</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -2687,10 +2687,10 @@
         <v>66</v>
       </c>
       <c r="J3" s="2">
-        <v>46225.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>85</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>88</v>
       </c>
       <c r="D4" s="2">
-        <v>46226.0</v>
+        <v>46226</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>90</v>
@@ -2716,10 +2716,10 @@
         <v>66</v>
       </c>
       <c r="J4" s="2">
-        <v>46226.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>100</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>88</v>
       </c>
       <c r="D5" s="2">
-        <v>46226.0</v>
+        <v>46226</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>65</v>
@@ -2739,10 +2739,10 @@
         <v>66</v>
       </c>
       <c r="J5" s="2">
-        <v>46226.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>112</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>115</v>
       </c>
       <c r="D6" s="2">
-        <v>46226.0</v>
+        <v>46226</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>119</v>
@@ -2769,45 +2769,47 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>270</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.5"/>
-    <col customWidth="1" min="2" max="2" width="20.88"/>
-    <col customWidth="1" min="5" max="5" width="29.75"/>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" customWidth="1"/>
+    <col min="5" max="5" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2831,6 +2833,6 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>